--- a/reports/Follow-up of Deployments ADaPT_v0.8.14.xlsx
+++ b/reports/Follow-up of Deployments ADaPT_v0.8.14.xlsx
@@ -620,7 +620,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-29 00:23:05 UTC</t>
+          <t>2026-10-29 23:11:18 UTC</t>
         </is>
       </c>
     </row>
